--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\githubレベニューツール\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\自社システム\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CDBCA1-00C9-4544-8A01-835EF11829A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C0EB94-E6B8-4112-8EBC-498F8E265AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="77">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -836,7 +836,7 @@
   <dimension ref="A1:C220"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.58203125" customWidth="1"/>
     <col min="2" max="2" width="10.4140625" customWidth="1"/>
     <col min="3" max="3" width="51.83203125" customWidth="1"/>
   </cols>
@@ -2591,54 +2591,70 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160" s="3"/>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A161" s="3"/>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" s="3">
+        <v>46417</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C160" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" s="3">
+        <v>46418</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C161" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="3"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="3"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="3"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="3"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="3"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="3"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="3"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="3"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="3"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="3"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="3"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="3"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="3"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="3"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="3"/>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.55000000000000004">

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\自社システム\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C0EB94-E6B8-4112-8EBC-498F8E265AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86872C19-40C2-4400-A1A3-BBAC997BCAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="78">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -413,6 +413,10 @@
   </si>
   <si>
     <t>LE SSERAFIM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Kis-My-Ft2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2613,10 +2617,26 @@
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162" s="3"/>
+      <c r="A162" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C162" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A163" s="3"/>
+      <c r="A163" s="3">
+        <v>46382</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\自社システム\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86872C19-40C2-4400-A1A3-BBAC997BCAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820F1CB0-1B3C-41B9-AF9F-AFF6B6D9080B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="80">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -417,6 +417,14 @@
   </si>
   <si>
     <t>Kis-My-Ft2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BE:FIRST</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LAPOSTA 2027</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2639,16 +2647,48 @@
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164" s="3"/>
+      <c r="A164" s="3">
+        <v>46403</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165" s="3"/>
+      <c r="A165" s="3">
+        <v>46404</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C165" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166" s="3"/>
+      <c r="A166" s="3">
+        <v>46424</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C166" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167" s="3"/>
+      <c r="A167" s="3">
+        <v>46425</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C167" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="3"/>

--- a/event_data.xlsx
+++ b/event_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\自社システム\githubレベニューツール\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tmizu\OneDrive\ドキュメント\自社システム（社内ツール）\githubレベニューツール\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820F1CB0-1B3C-41B9-AF9F-AFF6B6D9080B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FBA47C-A4A3-437D-A0A9-9264EA85F0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
+    <workbookView xWindow="1040" yWindow="460" windowWidth="21600" windowHeight="11180" xr2:uid="{86685B32-756C-410B-86C7-1E0CBD1BEB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="80">
   <si>
     <t>date</t>
     <phoneticPr fontId="1"/>
@@ -2691,10 +2691,26 @@
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168" s="3"/>
+      <c r="A168" s="3">
+        <v>46387</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C168" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A169" s="3"/>
+      <c r="A169" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C169" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="3"/>
